--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1217-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1217-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08652BAE-64BF-4515-8F90-29309B2E625A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{16841EAF-98D0-4816-9B3C-98A96DF6D0B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{9A71CE4D-F088-4795-848C-6EFF53E97AC5}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{8AD0A3A6-78DD-445F-9ECF-2A04EC7550FE}"/>
   </bookViews>
   <sheets>
     <sheet name="1217-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1532,25 +1532,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A63FA2EA-38C0-45E5-ADC8-F699EC17AE80}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69F2561B-5456-45B5-B5F4-EE7FDC7FC69C}">
   <dimension ref="A1:X49"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="10" width="6.625" customWidth="1"/>
-    <col min="11" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="15" width="6.625" customWidth="1"/>
-    <col min="16" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="8.25" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1584,7 +1582,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1620,7 +1618,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1672,7 +1670,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1740,7 +1738,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1812,7 +1810,7 @@
         <v>3.66</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1884,7 +1882,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -1956,7 +1954,7 @@
         <v>3.81</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2028,7 +2026,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2100,7 +2098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2172,7 +2170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2244,7 +2242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2017</v>
       </c>
@@ -2316,7 +2314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2016</v>
       </c>
@@ -2388,7 +2386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2015</v>
       </c>
@@ -2460,7 +2458,7 @@
         <v>2.12</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2014</v>
       </c>
@@ -2532,7 +2530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2013</v>
       </c>
@@ -2604,7 +2602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2012</v>
       </c>
@@ -2676,7 +2674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2011</v>
       </c>
@@ -2748,7 +2746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2010</v>
       </c>
@@ -2820,7 +2818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>2009</v>
       </c>
@@ -2892,7 +2890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2008</v>
       </c>
@@ -2964,7 +2962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2007</v>
       </c>
@@ -3036,7 +3034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2006</v>
       </c>
@@ -3108,7 +3106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <v>2005</v>
       </c>
@@ -3180,7 +3178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2004</v>
       </c>
@@ -3252,7 +3250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <v>2003</v>
       </c>
@@ -3324,7 +3322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2002</v>
       </c>
@@ -3396,7 +3394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="39">
         <v>2001</v>
       </c>
@@ -3468,7 +3466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2000</v>
       </c>
@@ -3540,7 +3538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="39">
         <v>1999</v>
       </c>
@@ -3612,7 +3610,7 @@
         <v>7.58</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>1998</v>
       </c>
@@ -3684,7 +3682,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="39">
         <v>1997</v>
       </c>
@@ -3756,7 +3754,7 @@
         <v>9.73</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>1996</v>
       </c>
@@ -3828,7 +3826,7 @@
         <v>8.43</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="39">
         <v>1995</v>
       </c>
@@ -3900,7 +3898,7 @@
         <v>3.63</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>1994</v>
       </c>
@@ -3972,7 +3970,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="41">
         <v>1993</v>
       </c>
@@ -4044,7 +4042,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="43"/>
       <c r="B37" s="44"/>
       <c r="C37" s="18" t="s">
@@ -4072,7 +4070,7 @@
       <c r="W37" s="50"/>
       <c r="X37" s="46"/>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="51">
         <v>1992</v>
       </c>
@@ -4144,7 +4142,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="53"/>
       <c r="B39" s="54"/>
       <c r="C39" s="20" t="s">
@@ -4172,7 +4170,7 @@
       <c r="W39" s="60"/>
       <c r="X39" s="56"/>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="41">
         <v>1991</v>
       </c>
@@ -4244,7 +4242,7 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="43"/>
       <c r="B41" s="44"/>
       <c r="C41" s="18" t="s">
@@ -4272,7 +4270,7 @@
       <c r="W41" s="50"/>
       <c r="X41" s="46"/>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="51">
         <v>1990</v>
       </c>
@@ -4344,7 +4342,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="53"/>
       <c r="B43" s="54"/>
       <c r="C43" s="20" t="s">
@@ -4372,7 +4370,7 @@
       <c r="W43" s="60"/>
       <c r="X43" s="56"/>
     </row>
-    <row r="44" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="39">
         <v>1989</v>
       </c>
@@ -4444,7 +4442,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="37">
         <v>1988</v>
       </c>
@@ -4516,7 +4514,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="39">
         <v>1987</v>
       </c>
@@ -4588,7 +4586,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="37">
         <v>1985</v>
       </c>
@@ -4660,7 +4658,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="39">
         <v>1984</v>
       </c>
@@ -4732,7 +4730,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="37" t="s">
         <v>46</v>
       </c>
